--- a/docs/S1_AnthracoForm_data_dictionary_v1.3.xlsx
+++ b/docs/S1_AnthracoForm_data_dictionary_v1.3.xlsx
@@ -530,7 +530,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Template — the header row of an empty file. The same header is supplied as S1_AnthracoForm_template_v1.3.csv, ready to use.</t>
+          <t>Template — the header row of an empty file, with the 220 columns in the right order, for converting existing datasets (user guide S2, section 9.1).</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Cumulative number of taxa in the SU at this fragment (saturation curve). Computed only on HF and LF fragments, in id_det order. Undetermined fragments, determinations covering several taxa (containing "/") and determinations with "cf." do not add a taxon. Empty for the other channels.</t>
+          <t>Cumulative number of taxa in the SU at this fragment (saturation curve). Computed only on HF and LF fragments with a taxon, in id_det order. Undetermined fragments, determinations covering several taxa (containing "/") and determinations with "cf." are not on the curve (Kabukcu &amp; Chabal 2021): the cell is empty for them, as for the other channels. Files saved before v1.3.1 also give a value to those fragments; it is recomputed when the SU is saved again.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
